--- a/data/derived_data/6_NMI_CCA/Dataset_2/CCA_NULL_ITS_D2.xlsx
+++ b/data/derived_data/6_NMI_CCA/Dataset_2/CCA_NULL_ITS_D2.xlsx
@@ -416,7 +416,7 @@
         <v>18.8227462005675</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +433,7 @@
         <v>12.9622303502903</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="4">
@@ -450,7 +450,7 @@
         <v>13.8634485749429</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="5">
@@ -467,7 +467,7 @@
         <v>8.55583080840544</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         <v>8.00800590138213</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
     </row>
   </sheetData>
